--- a/downloads/uttar-pradesh.xlsx
+++ b/downloads/uttar-pradesh.xlsx
@@ -720,7 +720,7 @@
         <v>1200138</v>
       </c>
       <c r="E2" t="n">
-        <v>30.04</v>
+        <v>30.0445</v>
       </c>
       <c r="F2" t="n">
         <v>128242</v>
@@ -738,19 +738,19 @@
         <v>59290</v>
       </c>
       <c r="K2" t="n">
-        <v>10.69</v>
+        <v>10.6856</v>
       </c>
       <c r="L2" t="n">
-        <v>35.64</v>
+        <v>35.638</v>
       </c>
       <c r="M2" t="n">
-        <v>44.65</v>
+        <v>44.6494</v>
       </c>
       <c r="N2" t="n">
-        <v>4.09</v>
+        <v>4.0867</v>
       </c>
       <c r="O2" t="n">
-        <v>4.94</v>
+        <v>4.9403</v>
       </c>
     </row>
     <row r="3">
@@ -769,7 +769,7 @@
         <v>818139</v>
       </c>
       <c r="E3" t="n">
-        <v>28.83</v>
+        <v>28.8281</v>
       </c>
       <c r="F3" t="n">
         <v>63824</v>
@@ -787,19 +787,19 @@
         <v>42618</v>
       </c>
       <c r="K3" t="n">
-        <v>7.8</v>
+        <v>7.8011</v>
       </c>
       <c r="L3" t="n">
-        <v>39.11</v>
+        <v>39.1099</v>
       </c>
       <c r="M3" t="n">
-        <v>43.99</v>
+        <v>43.9946</v>
       </c>
       <c r="N3" t="n">
-        <v>3.89</v>
+        <v>3.8853</v>
       </c>
       <c r="O3" t="n">
-        <v>5.21</v>
+        <v>5.2091</v>
       </c>
     </row>
     <row r="4">
@@ -818,7 +818,7 @@
         <v>411200</v>
       </c>
       <c r="E4" t="n">
-        <v>25.98</v>
+        <v>25.9756</v>
       </c>
       <c r="F4" t="n">
         <v>63139</v>
@@ -836,19 +836,19 @@
         <v>17877</v>
       </c>
       <c r="K4" t="n">
-        <v>15.35</v>
+        <v>15.3548</v>
       </c>
       <c r="L4" t="n">
-        <v>38.84</v>
+        <v>38.8427</v>
       </c>
       <c r="M4" t="n">
-        <v>32.43</v>
+        <v>32.4346</v>
       </c>
       <c r="N4" t="n">
-        <v>9.02</v>
+        <v>9.0204</v>
       </c>
       <c r="O4" t="n">
-        <v>4.35</v>
+        <v>4.3475</v>
       </c>
     </row>
     <row r="5">
@@ -867,7 +867,7 @@
         <v>902148</v>
       </c>
       <c r="E5" t="n">
-        <v>25.5</v>
+        <v>25.4969</v>
       </c>
       <c r="F5" t="n">
         <v>104046</v>
@@ -885,19 +885,19 @@
         <v>28939</v>
       </c>
       <c r="K5" t="n">
-        <v>11.53</v>
+        <v>11.5331</v>
       </c>
       <c r="L5" t="n">
-        <v>34.37</v>
+        <v>34.3686</v>
       </c>
       <c r="M5" t="n">
-        <v>43.41</v>
+        <v>43.4105</v>
       </c>
       <c r="N5" t="n">
-        <v>7.48</v>
+        <v>7.4799</v>
       </c>
       <c r="O5" t="n">
-        <v>3.21</v>
+        <v>3.2078</v>
       </c>
     </row>
     <row r="6">
@@ -916,7 +916,7 @@
         <v>665635</v>
       </c>
       <c r="E6" t="n">
-        <v>24.65</v>
+        <v>24.6548</v>
       </c>
       <c r="F6" t="n">
         <v>88663</v>
@@ -934,19 +934,19 @@
         <v>43325</v>
       </c>
       <c r="K6" t="n">
-        <v>13.32</v>
+        <v>13.3201</v>
       </c>
       <c r="L6" t="n">
-        <v>27.19</v>
+        <v>27.1931</v>
       </c>
       <c r="M6" t="n">
-        <v>47.03</v>
+        <v>47.0261</v>
       </c>
       <c r="N6" t="n">
-        <v>5.95</v>
+        <v>5.9519</v>
       </c>
       <c r="O6" t="n">
-        <v>6.51</v>
+        <v>6.5088</v>
       </c>
     </row>
     <row r="7">
@@ -965,7 +965,7 @@
         <v>1156305</v>
       </c>
       <c r="E7" t="n">
-        <v>24.64</v>
+        <v>24.6397</v>
       </c>
       <c r="F7" t="n">
         <v>173812</v>
@@ -983,19 +983,19 @@
         <v>19311</v>
       </c>
       <c r="K7" t="n">
-        <v>15.03</v>
+        <v>15.0317</v>
       </c>
       <c r="L7" t="n">
-        <v>31.75</v>
+        <v>31.7508</v>
       </c>
       <c r="M7" t="n">
-        <v>42.29</v>
+        <v>42.2863</v>
       </c>
       <c r="N7" t="n">
-        <v>9.26</v>
+        <v>9.261100000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>1.67</v>
+        <v>1.6701</v>
       </c>
     </row>
     <row r="8">
@@ -1014,7 +1014,7 @@
         <v>447471</v>
       </c>
       <c r="E8" t="n">
-        <v>23.98</v>
+        <v>23.9844</v>
       </c>
       <c r="F8" t="n">
         <v>37554</v>
@@ -1032,19 +1032,19 @@
         <v>12252</v>
       </c>
       <c r="K8" t="n">
-        <v>8.390000000000001</v>
+        <v>8.3925</v>
       </c>
       <c r="L8" t="n">
-        <v>31.73</v>
+        <v>31.7297</v>
       </c>
       <c r="M8" t="n">
-        <v>49.2</v>
+        <v>49.2012</v>
       </c>
       <c r="N8" t="n">
-        <v>7.94</v>
+        <v>7.9386</v>
       </c>
       <c r="O8" t="n">
-        <v>2.74</v>
+        <v>2.7381</v>
       </c>
     </row>
     <row r="9">
@@ -1063,7 +1063,7 @@
         <v>836943</v>
       </c>
       <c r="E9" t="n">
-        <v>23.25</v>
+        <v>23.248</v>
       </c>
       <c r="F9" t="n">
         <v>106358</v>
@@ -1081,19 +1081,19 @@
         <v>43145</v>
       </c>
       <c r="K9" t="n">
-        <v>12.71</v>
+        <v>12.7079</v>
       </c>
       <c r="L9" t="n">
-        <v>35.39</v>
+        <v>35.393</v>
       </c>
       <c r="M9" t="n">
-        <v>40.22</v>
+        <v>40.2211</v>
       </c>
       <c r="N9" t="n">
-        <v>6.52</v>
+        <v>6.5229</v>
       </c>
       <c r="O9" t="n">
-        <v>5.16</v>
+        <v>5.1551</v>
       </c>
     </row>
     <row r="10">
@@ -1112,7 +1112,7 @@
         <v>257903</v>
       </c>
       <c r="E10" t="n">
-        <v>22.3</v>
+        <v>22.2965</v>
       </c>
       <c r="F10" t="n">
         <v>35716</v>
@@ -1130,19 +1130,19 @@
         <v>23978</v>
       </c>
       <c r="K10" t="n">
-        <v>13.85</v>
+        <v>13.8486</v>
       </c>
       <c r="L10" t="n">
-        <v>21.89</v>
+        <v>21.8896</v>
       </c>
       <c r="M10" t="n">
-        <v>47.1</v>
+        <v>47.1041</v>
       </c>
       <c r="N10" t="n">
-        <v>7.86</v>
+        <v>7.8603</v>
       </c>
       <c r="O10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.2973</v>
       </c>
     </row>
     <row r="11">
@@ -1161,7 +1161,7 @@
         <v>503922</v>
       </c>
       <c r="E11" t="n">
-        <v>21.76</v>
+        <v>21.7626</v>
       </c>
       <c r="F11" t="n">
         <v>96544</v>
@@ -1179,19 +1179,19 @@
         <v>4199</v>
       </c>
       <c r="K11" t="n">
-        <v>19.16</v>
+        <v>19.1585</v>
       </c>
       <c r="L11" t="n">
-        <v>31.11</v>
+        <v>31.1133</v>
       </c>
       <c r="M11" t="n">
-        <v>38.74</v>
+        <v>38.7379</v>
       </c>
       <c r="N11" t="n">
-        <v>10.16</v>
+        <v>10.1569</v>
       </c>
       <c r="O11" t="n">
-        <v>0.83</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="12">
@@ -1210,7 +1210,7 @@
         <v>278095</v>
       </c>
       <c r="E12" t="n">
-        <v>21.57</v>
+        <v>21.5708</v>
       </c>
       <c r="F12" t="n">
         <v>38044</v>
@@ -1228,19 +1228,19 @@
         <v>3787</v>
       </c>
       <c r="K12" t="n">
-        <v>13.68</v>
+        <v>13.6802</v>
       </c>
       <c r="L12" t="n">
-        <v>35.21</v>
+        <v>35.2052</v>
       </c>
       <c r="M12" t="n">
-        <v>42.59</v>
+        <v>42.5934</v>
       </c>
       <c r="N12" t="n">
-        <v>7.16</v>
+        <v>7.1594</v>
       </c>
       <c r="O12" t="n">
-        <v>1.36</v>
+        <v>1.3618</v>
       </c>
     </row>
     <row r="13">
@@ -1259,7 +1259,7 @@
         <v>714753</v>
       </c>
       <c r="E13" t="n">
-        <v>20.99</v>
+        <v>20.9862</v>
       </c>
       <c r="F13" t="n">
         <v>115270</v>
@@ -1277,19 +1277,19 @@
         <v>11983</v>
       </c>
       <c r="K13" t="n">
-        <v>16.13</v>
+        <v>16.1272</v>
       </c>
       <c r="L13" t="n">
-        <v>32.9</v>
+        <v>32.8978</v>
       </c>
       <c r="M13" t="n">
-        <v>40.88</v>
+        <v>40.8782</v>
       </c>
       <c r="N13" t="n">
-        <v>8.42</v>
+        <v>8.420299999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>1.68</v>
+        <v>1.6765</v>
       </c>
     </row>
     <row r="14">
@@ -1308,7 +1308,7 @@
         <v>290824</v>
       </c>
       <c r="E14" t="n">
-        <v>20.8</v>
+        <v>20.8027</v>
       </c>
       <c r="F14" t="n">
         <v>39011</v>
@@ -1326,19 +1326,19 @@
         <v>6820</v>
       </c>
       <c r="K14" t="n">
-        <v>13.41</v>
+        <v>13.414</v>
       </c>
       <c r="L14" t="n">
-        <v>36.93</v>
+        <v>36.9271</v>
       </c>
       <c r="M14" t="n">
-        <v>38.82</v>
+        <v>38.8183</v>
       </c>
       <c r="N14" t="n">
-        <v>8.5</v>
+        <v>8.4955</v>
       </c>
       <c r="O14" t="n">
-        <v>2.35</v>
+        <v>2.3451</v>
       </c>
     </row>
     <row r="15">
@@ -1357,7 +1357,7 @@
         <v>541328</v>
       </c>
       <c r="E15" t="n">
-        <v>20.44</v>
+        <v>20.4402</v>
       </c>
       <c r="F15" t="n">
         <v>82235</v>
@@ -1375,19 +1375,19 @@
         <v>8380</v>
       </c>
       <c r="K15" t="n">
-        <v>15.19</v>
+        <v>15.1913</v>
       </c>
       <c r="L15" t="n">
-        <v>25.87</v>
+        <v>25.8725</v>
       </c>
       <c r="M15" t="n">
-        <v>41.15</v>
+        <v>41.1484</v>
       </c>
       <c r="N15" t="n">
-        <v>16.24</v>
+        <v>16.2397</v>
       </c>
       <c r="O15" t="n">
-        <v>1.55</v>
+        <v>1.548</v>
       </c>
     </row>
     <row r="16">
@@ -1406,7 +1406,7 @@
         <v>492995</v>
       </c>
       <c r="E16" t="n">
-        <v>20.39</v>
+        <v>20.3851</v>
       </c>
       <c r="F16" t="n">
         <v>82081</v>
@@ -1424,19 +1424,19 @@
         <v>6649</v>
       </c>
       <c r="K16" t="n">
-        <v>16.65</v>
+        <v>16.6495</v>
       </c>
       <c r="L16" t="n">
-        <v>37.66</v>
+        <v>37.6616</v>
       </c>
       <c r="M16" t="n">
-        <v>35.54</v>
+        <v>35.545</v>
       </c>
       <c r="N16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.795199999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>1.35</v>
+        <v>1.3487</v>
       </c>
     </row>
     <row r="17">
@@ -1455,7 +1455,7 @@
         <v>398900</v>
       </c>
       <c r="E17" t="n">
-        <v>20.33</v>
+        <v>20.3326</v>
       </c>
       <c r="F17" t="n">
         <v>77493</v>
@@ -1473,19 +1473,19 @@
         <v>9707</v>
       </c>
       <c r="K17" t="n">
-        <v>19.43</v>
+        <v>19.4267</v>
       </c>
       <c r="L17" t="n">
-        <v>26.15</v>
+        <v>26.1467</v>
       </c>
       <c r="M17" t="n">
-        <v>41.55</v>
+        <v>41.552</v>
       </c>
       <c r="N17" t="n">
-        <v>10.44</v>
+        <v>10.4412</v>
       </c>
       <c r="O17" t="n">
-        <v>2.43</v>
+        <v>2.4334</v>
       </c>
     </row>
     <row r="18">
@@ -1504,7 +1504,7 @@
         <v>318601</v>
       </c>
       <c r="E18" t="n">
-        <v>20.29</v>
+        <v>20.2891</v>
       </c>
       <c r="F18" t="n">
         <v>58138</v>
@@ -1522,19 +1522,19 @@
         <v>23348</v>
       </c>
       <c r="K18" t="n">
-        <v>18.25</v>
+        <v>18.2479</v>
       </c>
       <c r="L18" t="n">
-        <v>25.14</v>
+        <v>25.144</v>
       </c>
       <c r="M18" t="n">
-        <v>38.75</v>
+        <v>38.7491</v>
       </c>
       <c r="N18" t="n">
-        <v>10.53</v>
+        <v>10.5307</v>
       </c>
       <c r="O18" t="n">
-        <v>7.33</v>
+        <v>7.3283</v>
       </c>
     </row>
     <row r="19">
@@ -1553,7 +1553,7 @@
         <v>266870</v>
       </c>
       <c r="E19" t="n">
-        <v>19.96</v>
+        <v>19.9576</v>
       </c>
       <c r="F19" t="n">
         <v>43794</v>
@@ -1571,19 +1571,19 @@
         <v>3337</v>
       </c>
       <c r="K19" t="n">
-        <v>16.41</v>
+        <v>16.4102</v>
       </c>
       <c r="L19" t="n">
-        <v>21.56</v>
+        <v>21.5554</v>
       </c>
       <c r="M19" t="n">
-        <v>45.14</v>
+        <v>45.1373</v>
       </c>
       <c r="N19" t="n">
-        <v>15.65</v>
+        <v>15.6466</v>
       </c>
       <c r="O19" t="n">
-        <v>1.25</v>
+        <v>1.2504</v>
       </c>
     </row>
     <row r="20">
@@ -1602,7 +1602,7 @@
         <v>500109</v>
       </c>
       <c r="E20" t="n">
-        <v>19.81</v>
+        <v>19.8053</v>
       </c>
       <c r="F20" t="n">
         <v>88886</v>
@@ -1620,19 +1620,19 @@
         <v>15149</v>
       </c>
       <c r="K20" t="n">
-        <v>17.77</v>
+        <v>17.7733</v>
       </c>
       <c r="L20" t="n">
-        <v>24.4</v>
+        <v>24.4015</v>
       </c>
       <c r="M20" t="n">
-        <v>44.85</v>
+        <v>44.8512</v>
       </c>
       <c r="N20" t="n">
-        <v>9.94</v>
+        <v>9.944800000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>3.03</v>
+        <v>3.0291</v>
       </c>
     </row>
     <row r="21">
@@ -1651,7 +1651,7 @@
         <v>623772</v>
       </c>
       <c r="E21" t="n">
-        <v>19.55</v>
+        <v>19.549</v>
       </c>
       <c r="F21" t="n">
         <v>129101</v>
@@ -1669,19 +1669,19 @@
         <v>18964</v>
       </c>
       <c r="K21" t="n">
-        <v>20.7</v>
+        <v>20.6968</v>
       </c>
       <c r="L21" t="n">
-        <v>27.77</v>
+        <v>27.7709</v>
       </c>
       <c r="M21" t="n">
-        <v>39.58</v>
+        <v>39.5819</v>
       </c>
       <c r="N21" t="n">
-        <v>8.91</v>
+        <v>8.9101</v>
       </c>
       <c r="O21" t="n">
-        <v>3.04</v>
+        <v>3.0402</v>
       </c>
     </row>
     <row r="22">
@@ -1700,7 +1700,7 @@
         <v>373793</v>
       </c>
       <c r="E22" t="n">
-        <v>19.19</v>
+        <v>19.1948</v>
       </c>
       <c r="F22" t="n">
         <v>55893</v>
@@ -1718,19 +1718,19 @@
         <v>2628</v>
       </c>
       <c r="K22" t="n">
-        <v>14.95</v>
+        <v>14.9529</v>
       </c>
       <c r="L22" t="n">
-        <v>30.41</v>
+        <v>30.412</v>
       </c>
       <c r="M22" t="n">
-        <v>47.56</v>
+        <v>47.5587</v>
       </c>
       <c r="N22" t="n">
-        <v>6.37</v>
+        <v>6.3733</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7</v>
+        <v>0.7030999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1749,7 +1749,7 @@
         <v>233018</v>
       </c>
       <c r="E23" t="n">
-        <v>18.95</v>
+        <v>18.9502</v>
       </c>
       <c r="F23" t="n">
         <v>37966</v>
@@ -1767,19 +1767,19 @@
         <v>6078</v>
       </c>
       <c r="K23" t="n">
-        <v>16.29</v>
+        <v>16.2932</v>
       </c>
       <c r="L23" t="n">
-        <v>34.32</v>
+        <v>34.3188</v>
       </c>
       <c r="M23" t="n">
-        <v>40.49</v>
+        <v>40.4947</v>
       </c>
       <c r="N23" t="n">
-        <v>6.28</v>
+        <v>6.2849</v>
       </c>
       <c r="O23" t="n">
-        <v>2.61</v>
+        <v>2.6084</v>
       </c>
     </row>
     <row r="24">
@@ -1798,7 +1798,7 @@
         <v>502640</v>
       </c>
       <c r="E24" t="n">
-        <v>18.65</v>
+        <v>18.6506</v>
       </c>
       <c r="F24" t="n">
         <v>81672</v>
@@ -1816,117 +1816,117 @@
         <v>6559</v>
       </c>
       <c r="K24" t="n">
-        <v>16.25</v>
+        <v>16.2486</v>
       </c>
       <c r="L24" t="n">
-        <v>31.31</v>
+        <v>31.3129</v>
       </c>
       <c r="M24" t="n">
-        <v>39.19</v>
+        <v>39.1913</v>
       </c>
       <c r="N24" t="n">
-        <v>11.94</v>
+        <v>11.9423</v>
       </c>
       <c r="O24" t="n">
-        <v>1.3</v>
+        <v>1.3049</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aligarh</t>
+          <t>Amethi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2796379</v>
+        <v>1436528</v>
       </c>
       <c r="C25" t="n">
-        <v>2276190</v>
+        <v>1169287</v>
       </c>
       <c r="D25" t="n">
-        <v>520189</v>
+        <v>267241</v>
       </c>
       <c r="E25" t="n">
-        <v>18.6</v>
+        <v>18.6033</v>
       </c>
       <c r="F25" t="n">
-        <v>75500</v>
+        <v>56155</v>
       </c>
       <c r="G25" t="n">
-        <v>151351</v>
+        <v>59069</v>
       </c>
       <c r="H25" t="n">
-        <v>253497</v>
+        <v>123495</v>
       </c>
       <c r="I25" t="n">
-        <v>29940</v>
+        <v>24264</v>
       </c>
       <c r="J25" t="n">
-        <v>9901</v>
+        <v>4258</v>
       </c>
       <c r="K25" t="n">
-        <v>14.51</v>
+        <v>21.0129</v>
       </c>
       <c r="L25" t="n">
-        <v>29.1</v>
+        <v>22.1033</v>
       </c>
       <c r="M25" t="n">
-        <v>48.73</v>
+        <v>46.2111</v>
       </c>
       <c r="N25" t="n">
-        <v>5.76</v>
+        <v>9.0794</v>
       </c>
       <c r="O25" t="n">
-        <v>1.9</v>
+        <v>1.5933</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amethi</t>
+          <t>Aligarh</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1436528</v>
+        <v>2796379</v>
       </c>
       <c r="C26" t="n">
-        <v>1169287</v>
+        <v>2276190</v>
       </c>
       <c r="D26" t="n">
-        <v>267241</v>
+        <v>520189</v>
       </c>
       <c r="E26" t="n">
-        <v>18.6</v>
+        <v>18.6022</v>
       </c>
       <c r="F26" t="n">
-        <v>56155</v>
+        <v>75500</v>
       </c>
       <c r="G26" t="n">
-        <v>59069</v>
+        <v>151351</v>
       </c>
       <c r="H26" t="n">
-        <v>123495</v>
+        <v>253497</v>
       </c>
       <c r="I26" t="n">
-        <v>24264</v>
+        <v>29940</v>
       </c>
       <c r="J26" t="n">
-        <v>4258</v>
+        <v>9901</v>
       </c>
       <c r="K26" t="n">
-        <v>21.01</v>
+        <v>14.514</v>
       </c>
       <c r="L26" t="n">
-        <v>22.1</v>
+        <v>29.0954</v>
       </c>
       <c r="M26" t="n">
-        <v>46.21</v>
+        <v>48.7317</v>
       </c>
       <c r="N26" t="n">
-        <v>9.08</v>
+        <v>5.7556</v>
       </c>
       <c r="O26" t="n">
-        <v>1.59</v>
+        <v>1.9033</v>
       </c>
     </row>
     <row r="27">
@@ -1945,7 +1945,7 @@
         <v>469637</v>
       </c>
       <c r="E27" t="n">
-        <v>18.4</v>
+        <v>18.4027</v>
       </c>
       <c r="F27" t="n">
         <v>105356</v>
@@ -1963,19 +1963,19 @@
         <v>15481</v>
       </c>
       <c r="K27" t="n">
-        <v>22.43</v>
+        <v>22.4335</v>
       </c>
       <c r="L27" t="n">
-        <v>22.72</v>
+        <v>22.7163</v>
       </c>
       <c r="M27" t="n">
-        <v>41.17</v>
+        <v>41.1692</v>
       </c>
       <c r="N27" t="n">
-        <v>10.38</v>
+        <v>10.3846</v>
       </c>
       <c r="O27" t="n">
-        <v>3.3</v>
+        <v>3.2964</v>
       </c>
     </row>
     <row r="28">
@@ -1994,7 +1994,7 @@
         <v>321571</v>
       </c>
       <c r="E28" t="n">
-        <v>18.29</v>
+        <v>18.2946</v>
       </c>
       <c r="F28" t="n">
         <v>44891</v>
@@ -2012,19 +2012,19 @@
         <v>16730</v>
       </c>
       <c r="K28" t="n">
-        <v>13.96</v>
+        <v>13.9599</v>
       </c>
       <c r="L28" t="n">
-        <v>26.5</v>
+        <v>26.4959</v>
       </c>
       <c r="M28" t="n">
-        <v>42.43</v>
+        <v>42.4329</v>
       </c>
       <c r="N28" t="n">
-        <v>11.91</v>
+        <v>11.9087</v>
       </c>
       <c r="O28" t="n">
-        <v>5.2</v>
+        <v>5.2026</v>
       </c>
     </row>
     <row r="29">
@@ -2043,7 +2043,7 @@
         <v>573203</v>
       </c>
       <c r="E29" t="n">
-        <v>18.18</v>
+        <v>18.1755</v>
       </c>
       <c r="F29" t="n">
         <v>76243</v>
@@ -2061,19 +2061,19 @@
         <v>11121</v>
       </c>
       <c r="K29" t="n">
-        <v>13.3</v>
+        <v>13.3012</v>
       </c>
       <c r="L29" t="n">
-        <v>32.4</v>
+        <v>32.3983</v>
       </c>
       <c r="M29" t="n">
-        <v>44.15</v>
+        <v>44.1451</v>
       </c>
       <c r="N29" t="n">
-        <v>8.220000000000001</v>
+        <v>8.215199999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>1.94</v>
+        <v>1.9402</v>
       </c>
     </row>
     <row r="30">
@@ -2092,7 +2092,7 @@
         <v>455976</v>
       </c>
       <c r="E30" t="n">
-        <v>18.16</v>
+        <v>18.1621</v>
       </c>
       <c r="F30" t="n">
         <v>90556</v>
@@ -2110,19 +2110,19 @@
         <v>12757</v>
       </c>
       <c r="K30" t="n">
-        <v>19.86</v>
+        <v>19.8598</v>
       </c>
       <c r="L30" t="n">
-        <v>18.52</v>
+        <v>18.5242</v>
       </c>
       <c r="M30" t="n">
-        <v>48.34</v>
+        <v>48.3352</v>
       </c>
       <c r="N30" t="n">
-        <v>10.48</v>
+        <v>10.483</v>
       </c>
       <c r="O30" t="n">
-        <v>2.8</v>
+        <v>2.7977</v>
       </c>
     </row>
     <row r="31">
@@ -2141,7 +2141,7 @@
         <v>177299</v>
       </c>
       <c r="E31" t="n">
-        <v>18.15</v>
+        <v>18.151</v>
       </c>
       <c r="F31" t="n">
         <v>23654</v>
@@ -2159,19 +2159,19 @@
         <v>6989</v>
       </c>
       <c r="K31" t="n">
-        <v>13.34</v>
+        <v>13.3413</v>
       </c>
       <c r="L31" t="n">
-        <v>18.86</v>
+        <v>18.8552</v>
       </c>
       <c r="M31" t="n">
-        <v>56.81</v>
+        <v>56.8074</v>
       </c>
       <c r="N31" t="n">
-        <v>7.05</v>
+        <v>7.0542</v>
       </c>
       <c r="O31" t="n">
-        <v>3.94</v>
+        <v>3.9419</v>
       </c>
     </row>
     <row r="32">
@@ -2190,7 +2190,7 @@
         <v>344752</v>
       </c>
       <c r="E32" t="n">
-        <v>18.13</v>
+        <v>18.1256</v>
       </c>
       <c r="F32" t="n">
         <v>53433</v>
@@ -2208,19 +2208,19 @@
         <v>4819</v>
       </c>
       <c r="K32" t="n">
-        <v>15.5</v>
+        <v>15.499</v>
       </c>
       <c r="L32" t="n">
-        <v>25.02</v>
+        <v>25.0209</v>
       </c>
       <c r="M32" t="n">
-        <v>48.04</v>
+        <v>48.0383</v>
       </c>
       <c r="N32" t="n">
-        <v>10.04</v>
+        <v>10.044</v>
       </c>
       <c r="O32" t="n">
-        <v>1.4</v>
+        <v>1.3978</v>
       </c>
     </row>
     <row r="33">
@@ -2239,7 +2239,7 @@
         <v>544682</v>
       </c>
       <c r="E33" t="n">
-        <v>18.04</v>
+        <v>18.0393</v>
       </c>
       <c r="F33" t="n">
         <v>102212</v>
@@ -2257,19 +2257,19 @@
         <v>13280</v>
       </c>
       <c r="K33" t="n">
-        <v>18.77</v>
+        <v>18.7654</v>
       </c>
       <c r="L33" t="n">
-        <v>23.1</v>
+        <v>23.0975</v>
       </c>
       <c r="M33" t="n">
-        <v>46.24</v>
+        <v>46.2363</v>
       </c>
       <c r="N33" t="n">
-        <v>9.460000000000001</v>
+        <v>9.4626</v>
       </c>
       <c r="O33" t="n">
-        <v>2.44</v>
+        <v>2.4381</v>
       </c>
     </row>
     <row r="34">
@@ -2288,7 +2288,7 @@
         <v>219698</v>
       </c>
       <c r="E34" t="n">
-        <v>18</v>
+        <v>17.9963</v>
       </c>
       <c r="F34" t="n">
         <v>39830</v>
@@ -2306,19 +2306,19 @@
         <v>3298</v>
       </c>
       <c r="K34" t="n">
-        <v>18.13</v>
+        <v>18.1294</v>
       </c>
       <c r="L34" t="n">
-        <v>19.39</v>
+        <v>19.3948</v>
       </c>
       <c r="M34" t="n">
-        <v>47.1</v>
+        <v>47.1028</v>
       </c>
       <c r="N34" t="n">
-        <v>13.87</v>
+        <v>13.8718</v>
       </c>
       <c r="O34" t="n">
-        <v>1.5</v>
+        <v>1.5012</v>
       </c>
     </row>
     <row r="35">
@@ -2337,7 +2337,7 @@
         <v>342761</v>
       </c>
       <c r="E35" t="n">
-        <v>17.94</v>
+        <v>17.9428</v>
       </c>
       <c r="F35" t="n">
         <v>53833</v>
@@ -2355,19 +2355,19 @@
         <v>1944</v>
       </c>
       <c r="K35" t="n">
-        <v>15.71</v>
+        <v>15.7057</v>
       </c>
       <c r="L35" t="n">
-        <v>24.22</v>
+        <v>24.2221</v>
       </c>
       <c r="M35" t="n">
-        <v>49.39</v>
+        <v>49.3857</v>
       </c>
       <c r="N35" t="n">
-        <v>10.12</v>
+        <v>10.1193</v>
       </c>
       <c r="O35" t="n">
-        <v>0.57</v>
+        <v>0.5672</v>
       </c>
     </row>
     <row r="36">
@@ -2386,7 +2386,7 @@
         <v>251964</v>
       </c>
       <c r="E36" t="n">
-        <v>17.93</v>
+        <v>17.9324</v>
       </c>
       <c r="F36" t="n">
         <v>32884</v>
@@ -2404,19 +2404,19 @@
         <v>2977</v>
       </c>
       <c r="K36" t="n">
-        <v>13.05</v>
+        <v>13.0511</v>
       </c>
       <c r="L36" t="n">
-        <v>25.9</v>
+        <v>25.9009</v>
       </c>
       <c r="M36" t="n">
-        <v>48.83</v>
+        <v>48.8348</v>
       </c>
       <c r="N36" t="n">
-        <v>11.03</v>
+        <v>11.0317</v>
       </c>
       <c r="O36" t="n">
-        <v>1.18</v>
+        <v>1.1815</v>
       </c>
     </row>
     <row r="37">
@@ -2435,7 +2435,7 @@
         <v>337542</v>
       </c>
       <c r="E37" t="n">
-        <v>17.69</v>
+        <v>17.6927</v>
       </c>
       <c r="F37" t="n">
         <v>55414</v>
@@ -2453,19 +2453,19 @@
         <v>10095</v>
       </c>
       <c r="K37" t="n">
-        <v>16.42</v>
+        <v>16.4169</v>
       </c>
       <c r="L37" t="n">
-        <v>29.79</v>
+        <v>29.7877</v>
       </c>
       <c r="M37" t="n">
-        <v>43.71</v>
+        <v>43.7086</v>
       </c>
       <c r="N37" t="n">
-        <v>7.1</v>
+        <v>7.096</v>
       </c>
       <c r="O37" t="n">
-        <v>2.99</v>
+        <v>2.9907</v>
       </c>
     </row>
     <row r="38">
@@ -2484,7 +2484,7 @@
         <v>645625</v>
       </c>
       <c r="E38" t="n">
-        <v>17.61</v>
+        <v>17.6086</v>
       </c>
       <c r="F38" t="n">
         <v>132970</v>
@@ -2502,19 +2502,19 @@
         <v>8177</v>
       </c>
       <c r="K38" t="n">
-        <v>20.6</v>
+        <v>20.5955</v>
       </c>
       <c r="L38" t="n">
-        <v>16.33</v>
+        <v>16.327</v>
       </c>
       <c r="M38" t="n">
-        <v>49.6</v>
+        <v>49.5981</v>
       </c>
       <c r="N38" t="n">
-        <v>12.21</v>
+        <v>12.2128</v>
       </c>
       <c r="O38" t="n">
-        <v>1.27</v>
+        <v>1.2665</v>
       </c>
     </row>
     <row r="39">
@@ -2533,7 +2533,7 @@
         <v>300223</v>
       </c>
       <c r="E39" t="n">
-        <v>17.52</v>
+        <v>17.5226</v>
       </c>
       <c r="F39" t="n">
         <v>44116</v>
@@ -2551,19 +2551,19 @@
         <v>2227</v>
       </c>
       <c r="K39" t="n">
-        <v>14.69</v>
+        <v>14.6944</v>
       </c>
       <c r="L39" t="n">
-        <v>30.43</v>
+        <v>30.427</v>
       </c>
       <c r="M39" t="n">
-        <v>45.76</v>
+        <v>45.757</v>
       </c>
       <c r="N39" t="n">
-        <v>8.380000000000001</v>
+        <v>8.379799999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>0.74</v>
+        <v>0.7418</v>
       </c>
     </row>
     <row r="40">
@@ -2582,7 +2582,7 @@
         <v>407171</v>
       </c>
       <c r="E40" t="n">
-        <v>17.51</v>
+        <v>17.5123</v>
       </c>
       <c r="F40" t="n">
         <v>81809</v>
@@ -2600,19 +2600,19 @@
         <v>4429</v>
       </c>
       <c r="K40" t="n">
-        <v>20.09</v>
+        <v>20.092</v>
       </c>
       <c r="L40" t="n">
-        <v>20.91</v>
+        <v>20.9114</v>
       </c>
       <c r="M40" t="n">
-        <v>47.79</v>
+        <v>47.7853</v>
       </c>
       <c r="N40" t="n">
-        <v>10.12</v>
+        <v>10.1235</v>
       </c>
       <c r="O40" t="n">
-        <v>1.09</v>
+        <v>1.0877</v>
       </c>
     </row>
     <row r="41">
@@ -2631,7 +2631,7 @@
         <v>505802</v>
       </c>
       <c r="E41" t="n">
-        <v>17.5</v>
+        <v>17.5026</v>
       </c>
       <c r="F41" t="n">
         <v>89656</v>
@@ -2649,19 +2649,19 @@
         <v>9784</v>
       </c>
       <c r="K41" t="n">
-        <v>17.73</v>
+        <v>17.7255</v>
       </c>
       <c r="L41" t="n">
-        <v>37.01</v>
+        <v>37.0113</v>
       </c>
       <c r="M41" t="n">
-        <v>33.76</v>
+        <v>33.7636</v>
       </c>
       <c r="N41" t="n">
-        <v>9.57</v>
+        <v>9.565200000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>1.93</v>
+        <v>1.9344</v>
       </c>
     </row>
     <row r="42">
@@ -2680,7 +2680,7 @@
         <v>414799</v>
       </c>
       <c r="E42" t="n">
-        <v>17.22</v>
+        <v>17.2187</v>
       </c>
       <c r="F42" t="n">
         <v>67180</v>
@@ -2698,19 +2698,19 @@
         <v>15270</v>
       </c>
       <c r="K42" t="n">
-        <v>16.2</v>
+        <v>16.1958</v>
       </c>
       <c r="L42" t="n">
-        <v>20.3</v>
+        <v>20.2985</v>
       </c>
       <c r="M42" t="n">
-        <v>52.48</v>
+        <v>52.4833</v>
       </c>
       <c r="N42" t="n">
-        <v>7.34</v>
+        <v>7.3411</v>
       </c>
       <c r="O42" t="n">
-        <v>3.68</v>
+        <v>3.6813</v>
       </c>
     </row>
     <row r="43">
@@ -2747,19 +2747,19 @@
         <v>9337</v>
       </c>
       <c r="K43" t="n">
-        <v>18.52</v>
+        <v>18.5227</v>
       </c>
       <c r="L43" t="n">
-        <v>19.74</v>
+        <v>19.744</v>
       </c>
       <c r="M43" t="n">
-        <v>49.14</v>
+        <v>49.1353</v>
       </c>
       <c r="N43" t="n">
-        <v>9.65</v>
+        <v>9.652100000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>2.95</v>
+        <v>2.9459</v>
       </c>
     </row>
     <row r="44">
@@ -2778,7 +2778,7 @@
         <v>220426</v>
       </c>
       <c r="E44" t="n">
-        <v>16.8</v>
+        <v>16.8012</v>
       </c>
       <c r="F44" t="n">
         <v>32605</v>
@@ -2796,19 +2796,19 @@
         <v>9442</v>
       </c>
       <c r="K44" t="n">
-        <v>14.79</v>
+        <v>14.7918</v>
       </c>
       <c r="L44" t="n">
-        <v>28.87</v>
+        <v>28.8664</v>
       </c>
       <c r="M44" t="n">
-        <v>45.85</v>
+        <v>45.8494</v>
       </c>
       <c r="N44" t="n">
-        <v>6.21</v>
+        <v>6.2089</v>
       </c>
       <c r="O44" t="n">
-        <v>4.28</v>
+        <v>4.2835</v>
       </c>
     </row>
     <row r="45">
@@ -2827,7 +2827,7 @@
         <v>163458</v>
       </c>
       <c r="E45" t="n">
-        <v>16.75</v>
+        <v>16.7529</v>
       </c>
       <c r="F45" t="n">
         <v>27808</v>
@@ -2845,19 +2845,19 @@
         <v>1457</v>
       </c>
       <c r="K45" t="n">
-        <v>17.01</v>
+        <v>17.0123</v>
       </c>
       <c r="L45" t="n">
-        <v>28.03</v>
+        <v>28.0347</v>
       </c>
       <c r="M45" t="n">
-        <v>47.95</v>
+        <v>47.9548</v>
       </c>
       <c r="N45" t="n">
-        <v>6.11</v>
+        <v>6.1068</v>
       </c>
       <c r="O45" t="n">
-        <v>0.89</v>
+        <v>0.8914</v>
       </c>
     </row>
     <row r="46">
@@ -2876,7 +2876,7 @@
         <v>206320</v>
       </c>
       <c r="E46" t="n">
-        <v>16.73</v>
+        <v>16.7288</v>
       </c>
       <c r="F46" t="n">
         <v>34516</v>
@@ -2894,19 +2894,19 @@
         <v>2832</v>
       </c>
       <c r="K46" t="n">
-        <v>16.73</v>
+        <v>16.7294</v>
       </c>
       <c r="L46" t="n">
-        <v>17.93</v>
+        <v>17.928</v>
       </c>
       <c r="M46" t="n">
-        <v>51.44</v>
+        <v>51.4381</v>
       </c>
       <c r="N46" t="n">
-        <v>12.53</v>
+        <v>12.532</v>
       </c>
       <c r="O46" t="n">
-        <v>1.37</v>
+        <v>1.3726</v>
       </c>
     </row>
     <row r="47">
@@ -2925,7 +2925,7 @@
         <v>589543</v>
       </c>
       <c r="E47" t="n">
-        <v>16.51</v>
+        <v>16.5099</v>
       </c>
       <c r="F47" t="n">
         <v>103125</v>
@@ -2943,19 +2943,19 @@
         <v>10726</v>
       </c>
       <c r="K47" t="n">
-        <v>17.49</v>
+        <v>17.4924</v>
       </c>
       <c r="L47" t="n">
-        <v>22.84</v>
+        <v>22.8406</v>
       </c>
       <c r="M47" t="n">
-        <v>45.51</v>
+        <v>45.5059</v>
       </c>
       <c r="N47" t="n">
-        <v>12.34</v>
+        <v>12.3418</v>
       </c>
       <c r="O47" t="n">
-        <v>1.82</v>
+        <v>1.8194</v>
       </c>
     </row>
     <row r="48">
@@ -2974,7 +2974,7 @@
         <v>134992</v>
       </c>
       <c r="E48" t="n">
-        <v>16.51</v>
+        <v>16.5058</v>
       </c>
       <c r="F48" t="n">
         <v>28979</v>
@@ -2992,19 +2992,19 @@
         <v>1121</v>
       </c>
       <c r="K48" t="n">
-        <v>21.47</v>
+        <v>21.4672</v>
       </c>
       <c r="L48" t="n">
-        <v>21.58</v>
+        <v>21.5842</v>
       </c>
       <c r="M48" t="n">
-        <v>37.86</v>
+        <v>37.8645</v>
       </c>
       <c r="N48" t="n">
-        <v>18.25</v>
+        <v>18.2537</v>
       </c>
       <c r="O48" t="n">
-        <v>0.83</v>
+        <v>0.8304</v>
       </c>
     </row>
     <row r="49">
@@ -3023,7 +3023,7 @@
         <v>432534</v>
       </c>
       <c r="E49" t="n">
-        <v>16.37</v>
+        <v>16.3673</v>
       </c>
       <c r="F49" t="n">
         <v>74666</v>
@@ -3041,19 +3041,19 @@
         <v>14830</v>
       </c>
       <c r="K49" t="n">
-        <v>17.26</v>
+        <v>17.2625</v>
       </c>
       <c r="L49" t="n">
-        <v>20.81</v>
+        <v>20.8111</v>
       </c>
       <c r="M49" t="n">
-        <v>47.5</v>
+        <v>47.5047</v>
       </c>
       <c r="N49" t="n">
-        <v>10.99</v>
+        <v>10.9931</v>
       </c>
       <c r="O49" t="n">
-        <v>3.43</v>
+        <v>3.4286</v>
       </c>
     </row>
     <row r="50">
@@ -3072,7 +3072,7 @@
         <v>348862</v>
       </c>
       <c r="E50" t="n">
-        <v>16.35</v>
+        <v>16.3474</v>
       </c>
       <c r="F50" t="n">
         <v>67808</v>
@@ -3090,19 +3090,19 @@
         <v>5091</v>
       </c>
       <c r="K50" t="n">
-        <v>19.44</v>
+        <v>19.4369</v>
       </c>
       <c r="L50" t="n">
-        <v>21.82</v>
+        <v>21.8192</v>
       </c>
       <c r="M50" t="n">
-        <v>48.88</v>
+        <v>48.8755</v>
       </c>
       <c r="N50" t="n">
-        <v>8.41</v>
+        <v>8.4091</v>
       </c>
       <c r="O50" t="n">
-        <v>1.46</v>
+        <v>1.4593</v>
       </c>
     </row>
     <row r="51">
@@ -3121,7 +3121,7 @@
         <v>212059</v>
       </c>
       <c r="E51" t="n">
-        <v>16.34</v>
+        <v>16.3429</v>
       </c>
       <c r="F51" t="n">
         <v>32501</v>
@@ -3139,19 +3139,19 @@
         <v>6307</v>
       </c>
       <c r="K51" t="n">
-        <v>15.33</v>
+        <v>15.3264</v>
       </c>
       <c r="L51" t="n">
-        <v>33.08</v>
+        <v>33.0762</v>
       </c>
       <c r="M51" t="n">
-        <v>43.91</v>
+        <v>43.9095</v>
       </c>
       <c r="N51" t="n">
-        <v>4.71</v>
+        <v>4.7138</v>
       </c>
       <c r="O51" t="n">
-        <v>2.97</v>
+        <v>2.9742</v>
       </c>
     </row>
     <row r="52">
@@ -3170,7 +3170,7 @@
         <v>315468</v>
       </c>
       <c r="E52" t="n">
-        <v>16.32</v>
+        <v>16.3248</v>
       </c>
       <c r="F52" t="n">
         <v>61418</v>
@@ -3188,19 +3188,19 @@
         <v>2855</v>
       </c>
       <c r="K52" t="n">
-        <v>19.47</v>
+        <v>19.4689</v>
       </c>
       <c r="L52" t="n">
-        <v>23.63</v>
+        <v>23.6344</v>
       </c>
       <c r="M52" t="n">
-        <v>46.66</v>
+        <v>46.6554</v>
       </c>
       <c r="N52" t="n">
-        <v>9.34</v>
+        <v>9.3363</v>
       </c>
       <c r="O52" t="n">
-        <v>0.91</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="53">
@@ -3219,7 +3219,7 @@
         <v>189616</v>
       </c>
       <c r="E53" t="n">
-        <v>16.3</v>
+        <v>16.2967</v>
       </c>
       <c r="F53" t="n">
         <v>30114</v>
@@ -3237,19 +3237,19 @@
         <v>2346</v>
       </c>
       <c r="K53" t="n">
-        <v>15.88</v>
+        <v>15.8816</v>
       </c>
       <c r="L53" t="n">
-        <v>21.51</v>
+        <v>21.5108</v>
       </c>
       <c r="M53" t="n">
-        <v>51.55</v>
+        <v>51.5526</v>
       </c>
       <c r="N53" t="n">
-        <v>9.82</v>
+        <v>9.8177</v>
       </c>
       <c r="O53" t="n">
-        <v>1.24</v>
+        <v>1.2372</v>
       </c>
     </row>
     <row r="54">
@@ -3268,7 +3268,7 @@
         <v>344217</v>
       </c>
       <c r="E54" t="n">
-        <v>16.29</v>
+        <v>16.2936</v>
       </c>
       <c r="F54" t="n">
         <v>57185</v>
@@ -3286,19 +3286,19 @@
         <v>10500</v>
       </c>
       <c r="K54" t="n">
-        <v>16.61</v>
+        <v>16.6131</v>
       </c>
       <c r="L54" t="n">
-        <v>26.86</v>
+        <v>26.8572</v>
       </c>
       <c r="M54" t="n">
-        <v>45.36</v>
+        <v>45.3563</v>
       </c>
       <c r="N54" t="n">
-        <v>8.119999999999999</v>
+        <v>8.123100000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>3.05</v>
+        <v>3.0504</v>
       </c>
     </row>
     <row r="55">
@@ -3317,7 +3317,7 @@
         <v>172238</v>
       </c>
       <c r="E55" t="n">
-        <v>16.28</v>
+        <v>16.2809</v>
       </c>
       <c r="F55" t="n">
         <v>28524</v>
@@ -3335,19 +3335,19 @@
         <v>5211</v>
       </c>
       <c r="K55" t="n">
-        <v>16.56</v>
+        <v>16.5608</v>
       </c>
       <c r="L55" t="n">
-        <v>33.56</v>
+        <v>33.5588</v>
       </c>
       <c r="M55" t="n">
-        <v>40.67</v>
+        <v>40.6652</v>
       </c>
       <c r="N55" t="n">
-        <v>6.19</v>
+        <v>6.1897</v>
       </c>
       <c r="O55" t="n">
-        <v>3.03</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="56">
@@ -3366,7 +3366,7 @@
         <v>226875</v>
       </c>
       <c r="E56" t="n">
-        <v>16.17</v>
+        <v>16.1659</v>
       </c>
       <c r="F56" t="n">
         <v>38649</v>
@@ -3384,19 +3384,19 @@
         <v>3878</v>
       </c>
       <c r="K56" t="n">
-        <v>17.04</v>
+        <v>17.0354</v>
       </c>
       <c r="L56" t="n">
-        <v>29.64</v>
+        <v>29.6375</v>
       </c>
       <c r="M56" t="n">
-        <v>43.67</v>
+        <v>43.6655</v>
       </c>
       <c r="N56" t="n">
-        <v>7.95</v>
+        <v>7.9524</v>
       </c>
       <c r="O56" t="n">
-        <v>1.71</v>
+        <v>1.7093</v>
       </c>
     </row>
     <row r="57">
@@ -3415,7 +3415,7 @@
         <v>373154</v>
       </c>
       <c r="E57" t="n">
-        <v>16</v>
+        <v>16.0039</v>
       </c>
       <c r="F57" t="n">
         <v>71407</v>
@@ -3433,19 +3433,19 @@
         <v>7221</v>
       </c>
       <c r="K57" t="n">
-        <v>19.14</v>
+        <v>19.1361</v>
       </c>
       <c r="L57" t="n">
-        <v>24.21</v>
+        <v>24.2139</v>
       </c>
       <c r="M57" t="n">
-        <v>47.35</v>
+        <v>47.3518</v>
       </c>
       <c r="N57" t="n">
-        <v>7.36</v>
+        <v>7.3632</v>
       </c>
       <c r="O57" t="n">
-        <v>1.94</v>
+        <v>1.9351</v>
       </c>
     </row>
     <row r="58">
@@ -3482,19 +3482,19 @@
         <v>7241</v>
       </c>
       <c r="K58" t="n">
-        <v>13.95</v>
+        <v>13.9488</v>
       </c>
       <c r="L58" t="n">
-        <v>27.79</v>
+        <v>27.7923</v>
       </c>
       <c r="M58" t="n">
-        <v>43.87</v>
+        <v>43.8687</v>
       </c>
       <c r="N58" t="n">
-        <v>12.52</v>
+        <v>12.5221</v>
       </c>
       <c r="O58" t="n">
-        <v>1.87</v>
+        <v>1.8681</v>
       </c>
     </row>
     <row r="59">
@@ -3513,7 +3513,7 @@
         <v>298287</v>
       </c>
       <c r="E59" t="n">
-        <v>15.7</v>
+        <v>15.6958</v>
       </c>
       <c r="F59" t="n">
         <v>57467</v>
@@ -3531,19 +3531,19 @@
         <v>1084</v>
       </c>
       <c r="K59" t="n">
-        <v>19.27</v>
+        <v>19.2657</v>
       </c>
       <c r="L59" t="n">
-        <v>18.24</v>
+        <v>18.2388</v>
       </c>
       <c r="M59" t="n">
-        <v>49.64</v>
+        <v>49.6351</v>
       </c>
       <c r="N59" t="n">
-        <v>12.5</v>
+        <v>12.497</v>
       </c>
       <c r="O59" t="n">
-        <v>0.36</v>
+        <v>0.3634</v>
       </c>
     </row>
     <row r="60">
@@ -3562,7 +3562,7 @@
         <v>427159</v>
       </c>
       <c r="E60" t="n">
-        <v>15.53</v>
+        <v>15.5313</v>
       </c>
       <c r="F60" t="n">
         <v>72602</v>
@@ -3580,19 +3580,19 @@
         <v>10434</v>
       </c>
       <c r="K60" t="n">
-        <v>17</v>
+        <v>16.9965</v>
       </c>
       <c r="L60" t="n">
-        <v>18.68</v>
+        <v>18.682</v>
       </c>
       <c r="M60" t="n">
-        <v>54.33</v>
+        <v>54.3273</v>
       </c>
       <c r="N60" t="n">
-        <v>7.55</v>
+        <v>7.5515</v>
       </c>
       <c r="O60" t="n">
-        <v>2.44</v>
+        <v>2.4427</v>
       </c>
     </row>
     <row r="61">
@@ -3611,7 +3611,7 @@
         <v>230086</v>
       </c>
       <c r="E61" t="n">
-        <v>15.45</v>
+        <v>15.4542</v>
       </c>
       <c r="F61" t="n">
         <v>43054</v>
@@ -3629,19 +3629,19 @@
         <v>2954</v>
       </c>
       <c r="K61" t="n">
-        <v>18.71</v>
+        <v>18.7121</v>
       </c>
       <c r="L61" t="n">
-        <v>20.01</v>
+        <v>20.0143</v>
       </c>
       <c r="M61" t="n">
-        <v>47.83</v>
+        <v>47.8291</v>
       </c>
       <c r="N61" t="n">
-        <v>12.16</v>
+        <v>12.1607</v>
       </c>
       <c r="O61" t="n">
-        <v>1.28</v>
+        <v>1.2839</v>
       </c>
     </row>
     <row r="62">
@@ -3660,7 +3660,7 @@
         <v>158055</v>
       </c>
       <c r="E62" t="n">
-        <v>15.36</v>
+        <v>15.3648</v>
       </c>
       <c r="F62" t="n">
         <v>29715</v>
@@ -3678,19 +3678,19 @@
         <v>644</v>
       </c>
       <c r="K62" t="n">
-        <v>18.8</v>
+        <v>18.8004</v>
       </c>
       <c r="L62" t="n">
-        <v>25.71</v>
+        <v>25.7107</v>
       </c>
       <c r="M62" t="n">
-        <v>50.4</v>
+        <v>50.3995</v>
       </c>
       <c r="N62" t="n">
-        <v>4.68</v>
+        <v>4.6819</v>
       </c>
       <c r="O62" t="n">
-        <v>0.41</v>
+        <v>0.4075</v>
       </c>
     </row>
     <row r="63">
@@ -3709,7 +3709,7 @@
         <v>203957</v>
       </c>
       <c r="E63" t="n">
-        <v>15.26</v>
+        <v>15.2642</v>
       </c>
       <c r="F63" t="n">
         <v>35602</v>
@@ -3727,19 +3727,19 @@
         <v>1852</v>
       </c>
       <c r="K63" t="n">
-        <v>17.46</v>
+        <v>17.4556</v>
       </c>
       <c r="L63" t="n">
-        <v>25.55</v>
+        <v>25.5534</v>
       </c>
       <c r="M63" t="n">
-        <v>49.53</v>
+        <v>49.5345</v>
       </c>
       <c r="N63" t="n">
-        <v>6.55</v>
+        <v>6.5484</v>
       </c>
       <c r="O63" t="n">
-        <v>0.91</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="64">
@@ -3758,7 +3758,7 @@
         <v>566606</v>
       </c>
       <c r="E64" t="n">
-        <v>15.25</v>
+        <v>15.2549</v>
       </c>
       <c r="F64" t="n">
         <v>102383</v>
@@ -3776,19 +3776,19 @@
         <v>28642</v>
       </c>
       <c r="K64" t="n">
-        <v>18.07</v>
+        <v>18.0695</v>
       </c>
       <c r="L64" t="n">
-        <v>21.88</v>
+        <v>21.8831</v>
       </c>
       <c r="M64" t="n">
-        <v>46.54</v>
+        <v>46.5396</v>
       </c>
       <c r="N64" t="n">
-        <v>8.449999999999999</v>
+        <v>8.4528</v>
       </c>
       <c r="O64" t="n">
-        <v>5.06</v>
+        <v>5.055</v>
       </c>
     </row>
     <row r="65">
@@ -3807,7 +3807,7 @@
         <v>403369</v>
       </c>
       <c r="E65" t="n">
-        <v>15.14</v>
+        <v>15.1431</v>
       </c>
       <c r="F65" t="n">
         <v>57086</v>
@@ -3825,19 +3825,19 @@
         <v>7742</v>
       </c>
       <c r="K65" t="n">
-        <v>14.15</v>
+        <v>14.1523</v>
       </c>
       <c r="L65" t="n">
-        <v>19.12</v>
+        <v>19.1167</v>
       </c>
       <c r="M65" t="n">
         <v>58.33</v>
       </c>
       <c r="N65" t="n">
-        <v>6.48</v>
+        <v>6.4817</v>
       </c>
       <c r="O65" t="n">
-        <v>1.92</v>
+        <v>1.9193</v>
       </c>
     </row>
     <row r="66">
@@ -3856,7 +3856,7 @@
         <v>301022</v>
       </c>
       <c r="E66" t="n">
-        <v>15.11</v>
+        <v>15.1081</v>
       </c>
       <c r="F66" t="n">
         <v>57072</v>
@@ -3874,19 +3874,19 @@
         <v>2356</v>
       </c>
       <c r="K66" t="n">
-        <v>18.96</v>
+        <v>18.9594</v>
       </c>
       <c r="L66" t="n">
-        <v>23.87</v>
+        <v>23.873</v>
       </c>
       <c r="M66" t="n">
-        <v>43.3</v>
+        <v>43.3048</v>
       </c>
       <c r="N66" t="n">
-        <v>13.08</v>
+        <v>13.0801</v>
       </c>
       <c r="O66" t="n">
-        <v>0.78</v>
+        <v>0.7827</v>
       </c>
     </row>
     <row r="67">
@@ -3905,7 +3905,7 @@
         <v>219612</v>
       </c>
       <c r="E67" t="n">
-        <v>13.92</v>
+        <v>13.923</v>
       </c>
       <c r="F67" t="n">
         <v>37758</v>
@@ -3923,19 +3923,19 @@
         <v>10930</v>
       </c>
       <c r="K67" t="n">
-        <v>17.19</v>
+        <v>17.193</v>
       </c>
       <c r="L67" t="n">
-        <v>22.67</v>
+        <v>22.6659</v>
       </c>
       <c r="M67" t="n">
-        <v>49.68</v>
+        <v>49.6753</v>
       </c>
       <c r="N67" t="n">
-        <v>5.49</v>
+        <v>5.4888</v>
       </c>
       <c r="O67" t="n">
-        <v>4.98</v>
+        <v>4.977</v>
       </c>
     </row>
     <row r="68">
@@ -3954,7 +3954,7 @@
         <v>408689</v>
       </c>
       <c r="E68" t="n">
-        <v>13.85</v>
+        <v>13.8469</v>
       </c>
       <c r="F68" t="n">
         <v>74147</v>
@@ -3972,19 +3972,19 @@
         <v>1732</v>
       </c>
       <c r="K68" t="n">
-        <v>18.14</v>
+        <v>18.1426</v>
       </c>
       <c r="L68" t="n">
-        <v>20.26</v>
+        <v>20.2641</v>
       </c>
       <c r="M68" t="n">
-        <v>49.03</v>
+        <v>49.0324</v>
       </c>
       <c r="N68" t="n">
-        <v>12.14</v>
+        <v>12.1371</v>
       </c>
       <c r="O68" t="n">
-        <v>0.42</v>
+        <v>0.4238</v>
       </c>
     </row>
     <row r="69">
@@ -4003,7 +4003,7 @@
         <v>258547</v>
       </c>
       <c r="E69" t="n">
-        <v>13.82</v>
+        <v>13.8203</v>
       </c>
       <c r="F69" t="n">
         <v>44524</v>
@@ -4021,19 +4021,19 @@
         <v>6532</v>
       </c>
       <c r="K69" t="n">
-        <v>17.22</v>
+        <v>17.2209</v>
       </c>
       <c r="L69" t="n">
-        <v>17.89</v>
+        <v>17.8931</v>
       </c>
       <c r="M69" t="n">
-        <v>54.88</v>
+        <v>54.8798</v>
       </c>
       <c r="N69" t="n">
-        <v>7.48</v>
+        <v>7.4799</v>
       </c>
       <c r="O69" t="n">
-        <v>2.53</v>
+        <v>2.5264</v>
       </c>
     </row>
     <row r="70">
@@ -4052,7 +4052,7 @@
         <v>100992</v>
       </c>
       <c r="E70" t="n">
-        <v>13.67</v>
+        <v>13.667</v>
       </c>
       <c r="F70" t="n">
         <v>14835</v>
@@ -4070,19 +4070,19 @@
         <v>164</v>
       </c>
       <c r="K70" t="n">
-        <v>14.69</v>
+        <v>14.6893</v>
       </c>
       <c r="L70" t="n">
-        <v>32.05</v>
+        <v>32.052</v>
       </c>
       <c r="M70" t="n">
-        <v>45.52</v>
+        <v>45.5185</v>
       </c>
       <c r="N70" t="n">
-        <v>7.58</v>
+        <v>7.5778</v>
       </c>
       <c r="O70" t="n">
-        <v>0.16</v>
+        <v>0.1624</v>
       </c>
     </row>
     <row r="71">
@@ -4101,7 +4101,7 @@
         <v>199772</v>
       </c>
       <c r="E71" t="n">
-        <v>13.61</v>
+        <v>13.6086</v>
       </c>
       <c r="F71" t="n">
         <v>37093</v>
@@ -4119,19 +4119,19 @@
         <v>872</v>
       </c>
       <c r="K71" t="n">
-        <v>18.57</v>
+        <v>18.5677</v>
       </c>
       <c r="L71" t="n">
-        <v>26.47</v>
+        <v>26.4697</v>
       </c>
       <c r="M71" t="n">
-        <v>47.01</v>
+        <v>47.0066</v>
       </c>
       <c r="N71" t="n">
-        <v>7.52</v>
+        <v>7.5196</v>
       </c>
       <c r="O71" t="n">
-        <v>0.44</v>
+        <v>0.4365</v>
       </c>
     </row>
     <row r="72">
@@ -4150,7 +4150,7 @@
         <v>181177</v>
       </c>
       <c r="E72" t="n">
-        <v>13.22</v>
+        <v>13.221</v>
       </c>
       <c r="F72" t="n">
         <v>28124</v>
@@ -4168,19 +4168,19 @@
         <v>18258</v>
       </c>
       <c r="K72" t="n">
-        <v>15.52</v>
+        <v>15.5229</v>
       </c>
       <c r="L72" t="n">
-        <v>18.12</v>
+        <v>18.1187</v>
       </c>
       <c r="M72" t="n">
-        <v>47.36</v>
+        <v>47.3614</v>
       </c>
       <c r="N72" t="n">
-        <v>8.92</v>
+        <v>8.919499999999999</v>
       </c>
       <c r="O72" t="n">
-        <v>10.08</v>
+        <v>10.0774</v>
       </c>
     </row>
     <row r="73">
@@ -4199,7 +4199,7 @@
         <v>175421</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>12.9988</v>
       </c>
       <c r="F73" t="n">
         <v>30169</v>
@@ -4217,19 +4217,19 @@
         <v>4373</v>
       </c>
       <c r="K73" t="n">
-        <v>17.2</v>
+        <v>17.1981</v>
       </c>
       <c r="L73" t="n">
-        <v>30.22</v>
+        <v>30.2199</v>
       </c>
       <c r="M73" t="n">
-        <v>44.43</v>
+        <v>44.4285</v>
       </c>
       <c r="N73" t="n">
-        <v>5.66</v>
+        <v>5.6607</v>
       </c>
       <c r="O73" t="n">
-        <v>2.49</v>
+        <v>2.4929</v>
       </c>
     </row>
     <row r="74">
@@ -4248,7 +4248,7 @@
         <v>85352</v>
       </c>
       <c r="E74" t="n">
-        <v>12.42</v>
+        <v>12.4246</v>
       </c>
       <c r="F74" t="n">
         <v>14948</v>
@@ -4266,19 +4266,19 @@
         <v>163</v>
       </c>
       <c r="K74" t="n">
-        <v>17.51</v>
+        <v>17.5134</v>
       </c>
       <c r="L74" t="n">
-        <v>34.95</v>
+        <v>34.947</v>
       </c>
       <c r="M74" t="n">
-        <v>41.56</v>
+        <v>41.5643</v>
       </c>
       <c r="N74" t="n">
-        <v>5.78</v>
+        <v>5.7843</v>
       </c>
       <c r="O74" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="75">
@@ -4297,7 +4297,7 @@
         <v>90560</v>
       </c>
       <c r="E75" t="n">
-        <v>10.78</v>
+        <v>10.7844</v>
       </c>
       <c r="F75" t="n">
         <v>15195</v>
@@ -4315,19 +4315,19 @@
         <v>1918</v>
       </c>
       <c r="K75" t="n">
-        <v>16.78</v>
+        <v>16.7789</v>
       </c>
       <c r="L75" t="n">
-        <v>36.11</v>
+        <v>36.1076</v>
       </c>
       <c r="M75" t="n">
-        <v>41.68</v>
+        <v>41.6807</v>
       </c>
       <c r="N75" t="n">
-        <v>3.31</v>
+        <v>3.3149</v>
       </c>
       <c r="O75" t="n">
-        <v>2.12</v>
+        <v>2.1179</v>
       </c>
     </row>
     <row r="76">
@@ -4346,7 +4346,7 @@
         <v>95447</v>
       </c>
       <c r="E76" t="n">
-        <v>9.949999999999999</v>
+        <v>9.9549</v>
       </c>
       <c r="F76" t="n">
         <v>16769</v>
@@ -4364,19 +4364,19 @@
         <v>497</v>
       </c>
       <c r="K76" t="n">
-        <v>17.57</v>
+        <v>17.5689</v>
       </c>
       <c r="L76" t="n">
-        <v>20.52</v>
+        <v>20.5151</v>
       </c>
       <c r="M76" t="n">
-        <v>54.73</v>
+        <v>54.7319</v>
       </c>
       <c r="N76" t="n">
-        <v>6.66</v>
+        <v>6.6634</v>
       </c>
       <c r="O76" t="n">
-        <v>0.52</v>
+        <v>0.5207000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/uttar-pradesh.xlsx
+++ b/downloads/uttar-pradesh.xlsx
@@ -24758,7 +24758,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1 if the spread figure is larger than the 2022 margin, else 0. It says the removals were large enough to decide the seat, never that they did.</t>
+          <t>1 if the spread figure is larger than the 2022 margin, else 0. It says the names left off were large enough to decide the seat, never that they did.</t>
         </is>
       </c>
     </row>
